--- a/results/Int All Data -0.0/Rando_5_permute.xlsx
+++ b/results/Int All Data -0.0/Rando_5_permute.xlsx
@@ -440,147 +440,147 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7931733657269688</v>
+        <v>0.7719384725187284</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7931733657269688</v>
+        <v>0.7719384725187284</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7931733657269688</v>
+        <v>0.7712252057569594</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7931733657269688</v>
+        <v>0.763735904758386</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7923481300515552</v>
+        <v>0.7609339784424922</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7936827454327047</v>
+        <v>0.7609339784424922</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7943960121944735</v>
+        <v>0.76124983441217</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7940393788135891</v>
+        <v>0.7629618098141542</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7952827519210441</v>
+        <v>0.764785754129783</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7942128517783908</v>
+        <v>0.7651423875106675</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7961384016876891</v>
+        <v>0.7668439995926765</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.78147565566022</v>
+        <v>0.7691469095228096</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7811190222793356</v>
+        <v>0.7712459323969098</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7813941008378069</v>
+        <v>0.7718776443362654</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7835339011231135</v>
+        <v>0.7725909110980342</v>
       </c>
     </row>
     <row r="17">
@@ -590,1393 +590,1393 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.782912552503733</v>
+        <v>0.7752504544090519</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7839008978239732</v>
+        <v>0.7749449617593493</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7846445786769736</v>
+        <v>0.7734368734133983</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7843695001185023</v>
+        <v>0.7751384854954073</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7843695001185023</v>
+        <v>0.7785824870706319</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7804264821575171</v>
+        <v>0.7770743987246809</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7717656754226208</v>
+        <v>0.7823015672043278</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7787656474867146</v>
+        <v>0.7826582005852122</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7787656474867146</v>
+        <v>0.7826582005852122</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7748834577081923</v>
+        <v>0.7852769664850232</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7478097348522055</v>
+        <v>0.7620142419051206</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7468621669431721</v>
+        <v>0.7616576085242361</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7540356119720677</v>
+        <v>0.7469948624967671</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.749083522050892</v>
+        <v>0.7487780294011894</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.747708129258536</v>
+        <v>0.7487780294011894</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7470764173191804</v>
+        <v>0.7486556971675695</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7480550751881394</v>
+        <v>0.7486556971675695</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7438570294399391</v>
+        <v>0.7512336856561739</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7438570294399391</v>
+        <v>0.7466686432071141</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7735191041045055</v>
+        <v>0.7512129590162235</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7738045459829519</v>
+        <v>0.7519262257779924</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.772500344693034</v>
+        <v>0.7522828591588768</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7659178341922873</v>
+        <v>0.7495929017566278</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7623722270233931</v>
+        <v>0.7513352912498434</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7672323988021804</v>
+        <v>0.7538317249160346</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7684958226808918</v>
+        <v>0.7092525523054782</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7681391893000074</v>
+        <v>0.709170997483065</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7684550452696851</v>
+        <v>0.6975444789187543</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7511237443486112</v>
+        <v>0.697462924096341</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7520305348464381</v>
+        <v>0.6971062907154566</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7537321469284471</v>
+        <v>0.7006318471130945</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7525198637809176</v>
+        <v>0.6992053135895566</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7529172745730086</v>
+        <v>0.6992460910007633</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7500642075259331</v>
+        <v>0.6989302350310854</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7474253908548658</v>
+        <v>0.6989302350310854</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.732916067020942</v>
+        <v>0.7181988009188209</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7260280638704928</v>
+        <v>0.7241392361602368</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7210455598580856</v>
+        <v>0.7210926453771032</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7203322930963167</v>
+        <v>0.7248628662419808</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7168779282011168</v>
+        <v>0.7015289501596402</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.721860432213524</v>
+        <v>0.6950279944813068</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7174785501805471</v>
+        <v>0.6965360828272579</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7313768887150655</v>
+        <v>0.7000208618136892</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.736706338657076</v>
+        <v>0.7031897848304425</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7357283566568109</v>
+        <v>0.6999393069912759</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7353717232759265</v>
+        <v>0.7024357406574671</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7348312536102652</v>
+        <v>0.7023541858350538</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7396202338866145</v>
+        <v>0.7099250416560405</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7363490294074975</v>
+        <v>0.7117082085604628</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7361147282602328</v>
+        <v>0.7117082085604628</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7283613878918574</v>
+        <v>0.7122991430886118</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7196093388832667</v>
+        <v>0.7122991430886118</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7276584844500638</v>
+        <v>0.719115954736623</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7282901963894193</v>
+        <v>0.719115954736623</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7282901963894193</v>
+        <v>0.7277159332890564</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6760633442163213</v>
+        <v>0.7384557121267966</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6104572206657216</v>
+        <v>0.7340026385913815</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5931874237958048</v>
+        <v>0.723303637164848</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5878586497224882</v>
+        <v>0.7239353491042037</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5814295614152871</v>
+        <v>0.717872581629168</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.57598949429702</v>
+        <v>0.7174343934258702</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5497741246824543</v>
+        <v>0.726778728699998</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5564686040968457</v>
+        <v>0.7331780787846619</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5461580018798161</v>
+        <v>0.732658335758951</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5178262620946703</v>
+        <v>0.7316499396674546</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5179181802370587</v>
+        <v>0.732006573048339</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5054981918259539</v>
+        <v>0.7342175648360838</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5050600036226562</v>
+        <v>0.7313748611089834</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5033079266781595</v>
+        <v>0.7351043045626544</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5038988612063084</v>
+        <v>0.7386402242802674</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5024833668714399</v>
+        <v>0.7435211226990051</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5015164240598441</v>
+        <v>0.7366331195485558</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5015164240598441</v>
+        <v>0.7235904307806824</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4954640199047836</v>
+        <v>0.7262299233204438</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5003449183235212</v>
+        <v>0.7427172895322358</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5018018659382905</v>
+        <v>0.7154396796202158</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.4981947547182393</v>
+        <v>0.7447063710987732</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.4939766581987829</v>
+        <v>0.7333148295504212</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.4988368299775702</v>
+        <v>0.7278112307749149</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5026775664761919</v>
+        <v>0.7305723796796022</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.4973080149916688</v>
+        <v>0.7334351341779589</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.4946588350006263</v>
+        <v>0.7343730146357113</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.4920504324207904</v>
+        <v>0.7343322372245047</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.4851016010878783</v>
+        <v>0.7357587707480424</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.4905837973547401</v>
+        <v>0.736706338657076</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.4905022425323268</v>
+        <v>0.7291665727960147</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.4889229626839376</v>
+        <v>0.7066675798403688</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.4885255518918465</v>
+        <v>0.700064342699672</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.4915313652637736</v>
+        <v>0.7015012395431848</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.4955358872759157</v>
+        <v>0.7062715207856658</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.4966057874185691</v>
+        <v>0.698038538934092</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5025773126199103</v>
+        <v>0.708177019923708</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5023430114726458</v>
+        <v>0.6999233114321838</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5037695449961835</v>
+        <v>0.6984663638174144</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5037695449961835</v>
+        <v>0.6803596162147207</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.502159851056563</v>
+        <v>0.6712840513912532</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5011410916450915</v>
+        <v>0.6668413411758133</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5021702143765382</v>
+        <v>0.6680757027006812</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5014569476147692</v>
+        <v>0.6592725129609087</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4997145581215536</v>
+        <v>0.6567774310321055</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4997145581215536</v>
+        <v>0.6604149563433882</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5012226464675047</v>
+        <v>0.6561346799040808</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5008660130866203</v>
+        <v>0.6460299923491664</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5008660130866203</v>
+        <v>0.6313388598365479</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5008660130866203</v>
+        <v>0.5367161162241829</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.501181869056298</v>
+        <v>0.5076690820711861</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.501181869056298</v>
+        <v>0.5042361196846307</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5012634238787113</v>
+        <v>0.5043176745070439</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4996433666191156</v>
+        <v>0.5027992228411177</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4996433666191156</v>
+        <v>0.4976231950926526</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4996433666191156</v>
+        <v>0.4848555848832504</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4996433666191156</v>
+        <v>0.4848555848832504</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4996433666191156</v>
+        <v>0.4786587701172317</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4999592225887934</v>
+        <v>0.4837636063632587</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4999592225887934</v>
+        <v>0.4865357944566151</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5</v>
+        <v>0.4870652249336072</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5</v>
+        <v>0.5024633161001836</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5</v>
+        <v>0.5016484437447452</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5006317119393556</v>
+        <v>0.4973300933690072</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.4973300933690072</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.4989093732173963</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.4993883388319006</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.5014258576548438</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.499999324131306</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.4999689100400745</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.494374744859568</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.5009980327715212</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.5029443093207699</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.5029035319095634</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5</v>
+        <v>0.5012530605587362</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5</v>
+        <v>0.4964233028711803</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5</v>
+        <v>0.4957915909318247</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5006317119393556</v>
+        <v>0.4949152145252293</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5006317119393556</v>
+        <v>0.4988077676237268</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.4988077676237268</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.4998368903551735</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.4998368903551735</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5</v>
+        <v>0.4997553355327602</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5</v>
+        <v>0.4986446579789003</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B156" t="n">
